--- a/examples/excel/charts/charts-pie.xlsx
+++ b/examples/excel/charts/charts-pie.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Pie Charts" sheetId="2" r:id="Re9466078d28e4559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Doughnut Charts" sheetId="3" r:id="R3f4ca487b35248b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Pie Advanced" sheetId="4" r:id="Re87516badd5445d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Pie Charts" sheetId="2" r:id="R0c6d76ecfe534b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Doughnut Charts" sheetId="3" r:id="R467b66cadbaf4ea2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Pie Advanced" sheetId="4" r:id="R4d8763c3d16445ce"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -74,9 +74,18 @@
           </c:dPt>
           <c:cat>
             <c:strLit>
-              <c:ptCount val="1"/>
-              <c:pt idx="0">
-                <c:v>Product</c:v>
+              <c:ptCount val="4"/>
+              <c:pt idx="0">
+                <c:v>Product A</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Product B</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Product C</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>Product D</c:v>
               </c:pt>
             </c:strLit>
           </c:cat>
@@ -995,6 +1004,73 @@
             </c:numLit>
           </c:val>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>2025</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="12700">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="4472C4"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="70AD47"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FFC000"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strLit>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>Electronics</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>Clothing</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>Food</c:v>
+              </c:pt>
+            </c:strLit>
+          </c:cat>
+          <c:val>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="3"/>
+              <c:pt idx="0">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>30</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>25</c:v>
+              </c:pt>
+            </c:numLit>
+          </c:val>
+        </c:ser>
         <c:holeSize val="50"/>
       </c:doughnutChart>
     </c:plotArea>
@@ -1111,7 +1187,7 @@
           </c:val>
         </c:ser>
         <c:dLbls>
-          <c:numFmt formatCode="0%" sourceLinked="0"/>
+          <c:numFmt formatCode="0&quot;%&quot;" sourceLinked="0"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
           <c:showCatName val="0"/>
@@ -1357,7 +1433,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7207583305af47cc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R94efc2c19a874e1c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1387,7 +1463,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc8cb5388a73d4963"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4577b183a3f34353"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1417,7 +1493,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf4c2fecfdf084172"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68119f476e574754"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1452,7 +1528,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ref222689d5444f27"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R798eb81149f048d2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1482,7 +1558,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc62460e65331490e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3489a009baf34da8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1512,7 +1588,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69e8619a4c7148ae"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd97f31822e3d4967"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1542,7 +1618,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8c0d02e75e894055"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R731de213dc534ddc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1577,7 +1653,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R50ccb9aab9f744aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rabc7ab3328794d8c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1607,7 +1683,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R918ed831b8724591"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ree1a5338115541be"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1637,7 +1713,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24229d13de4b4c0b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3d6df853bec84b22"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1667,7 +1743,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd3e9ffdbb7a04d6f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R44b29f96847b407b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1676,23 +1752,132 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f79aeaea42d416a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4e906256eb44ae1"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f51ea0d69d6441b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06d27c3f4391407e"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbfb018e9c3d34784"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cc5fe3951814ec7"/>
 </x:worksheet>
 </file>